--- a/IBM_Cost_Data_Breach_2025.xlsx
+++ b/IBM_Cost_Data_Breach_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crook\PROJECTS\Trout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F1CD33-E637-4CC3-939C-AEDA1EE35824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D0BC85-5CEA-4F32-B8A4-732E40F26148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Highlights" sheetId="1" r:id="rId1"/>
@@ -1488,6 +1488,11 @@
     <row r="18" ht="25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D8:E8"/>
@@ -1497,11 +1502,6 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1509,101 +1509,101 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A20C47-89D7-4E1F-AFD1-BF552B7FF925}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A2:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B2" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="35"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="35"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="40">
+      <c r="B3" s="40">
         <v>3.86</v>
       </c>
-      <c r="C2" s="35"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="C3" s="35"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="39">
+      <c r="B4" s="39">
         <v>3.92</v>
       </c>
-      <c r="C3" s="35"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="C4" s="35"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="40">
+      <c r="B5" s="40">
         <v>3.86</v>
       </c>
-      <c r="C4" s="35"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+      <c r="C5" s="35"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="39">
+      <c r="B6" s="39">
         <v>4.24</v>
       </c>
-      <c r="C5" s="35"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="C6" s="35"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B7" s="40">
         <v>4.3499999999999996</v>
       </c>
-      <c r="C6" s="35"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="C7" s="35"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="39">
+      <c r="B8" s="39">
         <v>4.45</v>
       </c>
-      <c r="C7" s="35"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="C8" s="35"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="40">
+      <c r="B9" s="40">
         <v>4.88</v>
       </c>
-      <c r="C8" s="35"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="C9" s="35"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="39">
+      <c r="B10" s="39">
         <v>4.4400000000000004</v>
       </c>
-      <c r="C9" s="35"/>
+      <c r="C10" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1611,7 +1611,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A2:E18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1620,292 +1620,292 @@
     <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C3" s="8">
         <v>10.220000000000001</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D3" s="10">
         <v>9.36</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E3" s="11">
         <v>9.1880341880342012E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C4" s="9">
         <v>7.29</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D4" s="12">
         <v>8.75</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E4" s="13">
         <v>-0.16685714285714279</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C5" s="8">
         <v>6.24</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D5" s="10">
         <v>5.9</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E5" s="11">
         <v>5.7627118644067769E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C6" s="9">
         <v>4.84</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D6" s="12">
         <v>4.66</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E6" s="14">
         <v>3.8626609442060027E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C7" s="8">
         <v>4.1399999999999997</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D7" s="10">
         <v>4.53</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E7" s="15">
         <v>-8.60927152317882E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C8" s="9">
         <v>4.03</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D8" s="12">
         <v>5.31</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E8" s="13">
         <v>-0.2410546139359698</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C9" s="8">
         <v>3.81</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D9" s="10">
         <v>4.16</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E9" s="15">
         <v>-8.4134615384615405E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C10" s="9">
         <v>3.73</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D10" s="12">
         <v>4.17</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E10" s="13">
         <v>-0.105515587529976</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C11" s="8">
         <v>3.67</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D11" s="10">
         <v>3.23</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E11" s="11">
         <v>0.13622291021671831</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C12" s="9">
         <v>3.65</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D12" s="12">
         <v>4.1900000000000004</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E12" s="13">
         <v>-0.12887828162291179</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C13" s="8">
         <v>3.44</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D13" s="10">
         <v>4.7300000000000004</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E13" s="15">
         <v>-0.27272727272727282</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C14" s="9">
         <v>2.84</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D14" s="12">
         <v>3.62</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E14" s="13">
         <v>-0.2154696132596686</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C15" s="8">
         <v>2.5499999999999998</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D15" s="10">
         <v>2.78</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E15" s="15">
         <v>-8.2733812949640287E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C16" s="9">
         <v>2.5099999999999998</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D16" s="12">
         <v>2.35</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E16" s="14">
         <v>6.8085106382978586E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C17" s="8">
         <v>2.37</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D17" s="10">
         <v>2.78</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E17" s="15">
         <v>-0.1474820143884891</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C18" s="9">
         <v>1.22</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D18" s="12">
         <v>1.36</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E18" s="13">
         <v>-0.1029411764705883</v>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A2:E19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1925,309 +1925,309 @@
     <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C3" s="8">
         <v>7.42</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D3" s="10">
         <v>9.77</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E3" s="15">
         <v>-0.24053224155578301</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C4" s="9">
         <v>5.56</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D4" s="12">
         <v>6.08</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E4" s="13">
         <v>-8.5526315789473756E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C5" s="8">
         <v>5</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D5" s="10">
         <v>5.56</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E5" s="15">
         <v>-0.1007194244604316</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C6" s="9">
         <v>4.83</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D6" s="12">
         <v>5.29</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E6" s="13">
         <v>-8.6956521739130432E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C7" s="8">
         <v>4.79</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D7" s="10">
         <v>5.45</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E7" s="15">
         <v>-0.1211009174311927</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C8" s="9">
         <v>4.6100000000000003</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D8" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E8" s="13">
         <v>-9.60784313725489E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C9" s="8">
         <v>4.5599999999999996</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D9" s="10">
         <v>5.08</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E9" s="15">
         <v>-0.1023622047244095</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C10" s="9">
         <v>4.43</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D10" s="12">
         <v>4.09</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E10" s="14">
         <v>8.3129584352078206E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C11" s="8">
         <v>4.22</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D11" s="10">
         <v>3.94</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E11" s="11">
         <v>7.1065989847715685E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C12" s="9">
         <v>4.03</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D12" s="12">
         <v>3.82</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E12" s="14">
         <v>5.4973821989528902E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C13" s="8">
         <v>3.98</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D13" s="10">
         <v>4.43</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E13" s="15">
         <v>-0.10158013544018051</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B14" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C14" s="9">
         <v>3.8</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D14" s="12">
         <v>3.5</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E14" s="14">
         <v>8.571428571428566E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C15" s="8">
         <v>3.79</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D15" s="10">
         <v>3.54</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E15" s="11">
         <v>7.0621468926553674E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C16" s="9">
         <v>3.75</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D16" s="12">
         <v>4.09</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E16" s="13">
         <v>-8.3129584352078206E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C17" s="8">
         <v>3.72</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D17" s="10">
         <v>3.91</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E17" s="15">
         <v>-4.8593350383631703E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C18" s="9">
         <v>3.54</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D18" s="12">
         <v>3.48</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E18" s="14">
         <v>1.7241379310344841E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C19" s="8">
         <v>2.86</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D19" s="10">
         <v>2.5499999999999998</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E19" s="11">
         <v>0.1215686274509804</v>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A2:D26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2425,353 +2425,353 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+    <row r="3" spans="1:4" ht="25" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B10" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="13" spans="1:4" ht="25" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B14" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D18" s="6" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="5">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B20" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="5">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B22" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="5">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B24" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D24" s="6" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="5">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C26" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A2:D32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2790,437 +2790,437 @@
     <col min="3" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C3" s="18">
         <v>-227192</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C3" s="20">
-        <v>-223503</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" s="18">
-        <v>-212061</v>
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="20">
+        <v>-223503</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C5" s="20">
-        <v>-211906</v>
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="18">
+        <v>-212061</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="18">
-        <v>-208087</v>
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="20">
+        <v>-211906</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C7" s="20">
-        <v>-201201</v>
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" s="18">
+        <v>-208087</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="18">
-        <v>-196951</v>
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="20">
+        <v>-201201</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="20">
-        <v>-193242</v>
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="18">
+        <v>-196951</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C10" s="18">
-        <v>-192266</v>
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="20">
+        <v>-193242</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C11" s="20">
-        <v>-191893</v>
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="18">
+        <v>-192266</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C12" s="18">
-        <v>-189838</v>
+      <c r="A12" s="5">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="20">
+        <v>-191893</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C13" s="20">
-        <v>-186559</v>
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="18">
+        <v>-189838</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C14" s="18">
-        <v>-184109</v>
+      <c r="A14" s="5">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="20">
+        <v>-186559</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="20">
-        <v>-168361</v>
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="18">
+        <v>-184109</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C16" s="18">
-        <v>-162574</v>
+      <c r="A16" s="5">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" s="20">
+        <v>-168361</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C17" s="20">
-        <v>-160547</v>
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="18">
+        <v>-162574</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C18" s="18">
-        <v>-157456</v>
+      <c r="A18" s="5">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="20">
+        <v>-160547</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="5">
-        <v>18</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C19" s="20">
-        <v>-147097</v>
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C19" s="18">
+        <v>-157456</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C20" s="18">
-        <v>-128087</v>
+      <c r="A20" s="5">
+        <v>18</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="20">
+        <v>-147097</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="5">
-        <v>20</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C21" s="20">
-        <v>-113840</v>
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" s="18">
+        <v>-128087</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C22" s="18">
-        <v>-110772</v>
+      <c r="A22" s="5">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C22" s="20">
+        <v>-113840</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="5">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="18">
+        <v>-110772</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B24" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C24" s="21">
         <v>131212</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C24" s="23">
-        <v>173400</v>
       </c>
       <c r="D24" s="22" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="5">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C25" s="21">
-        <v>173692</v>
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="23">
+        <v>173400</v>
       </c>
       <c r="D25" s="22" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C26" s="23">
-        <v>174538</v>
+      <c r="A26" s="5">
+        <v>24</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="21">
+        <v>173692</v>
       </c>
       <c r="D26" s="22" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="5">
-        <v>26</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C27" s="21">
-        <v>175010</v>
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="23">
+        <v>174538</v>
       </c>
       <c r="D27" s="22" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C28" s="23">
-        <v>193511</v>
+      <c r="A28" s="5">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="21">
+        <v>175010</v>
       </c>
       <c r="D28" s="22" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="5">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C29" s="21">
-        <v>200321</v>
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="23">
+        <v>193511</v>
       </c>
       <c r="D29" s="22" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C30" s="23">
-        <v>207914</v>
+      <c r="A30" s="5">
+        <v>28</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C30" s="21">
+        <v>200321</v>
       </c>
       <c r="D30" s="22" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="5">
+      <c r="A31" s="2">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C31" s="23">
+        <v>207914</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B32" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C32" s="21">
         <v>227244</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D32" s="22" t="s">
         <v>198</v>
       </c>
     </row>
